--- a/output/pdf_financials_xlsx/TFPM.xlsx
+++ b/output/pdf_financials_xlsx/TFPM.xlsx
@@ -499,22 +499,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.112588</v>
+        <v>112.588</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.150421</v>
+        <v>150.421</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.151885</v>
+        <v>151.885</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.204024</v>
+        <v>204.024</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.268991</v>
+        <v>268.991</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.388704</v>
+        <v>388.704</v>
       </c>
     </row>
     <row r="5">
@@ -524,22 +524,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.06249</v>
+        <v>62.49</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.06716800000000001</v>
+        <v>67.16800000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.06488099999999999</v>
+        <v>64.881</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.101948</v>
+        <v>101.948</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.113781</v>
+        <v>113.781</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.125786</v>
+        <v>125.786</v>
       </c>
     </row>
     <row r="6">
@@ -549,22 +549,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.050098</v>
+        <v>50.098</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.08325299999999999</v>
+        <v>83.253</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.087004</v>
+        <v>87.004</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.102076</v>
+        <v>102.076</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.15521</v>
+        <v>155.21</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.262918</v>
+        <v>262.918</v>
       </c>
     </row>
     <row r="7">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.034663</v>
+        <v>34.663</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.068744</v>
+        <v>68.744</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.064107</v>
+        <v>64.107</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.040262</v>
+        <v>40.262</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.017984</v>
+        <v>-17.984</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.220819</v>
+        <v>220.819</v>
       </c>
     </row>
     <row r="12">
@@ -780,16 +780,16 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-0.004732</v>
+        <v>-4.732</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-0.004543</v>
+        <v>-4.543</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.003448</v>
+        <v>3.448</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.03824</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="16">
@@ -799,22 +799,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.06216</v>
+        <v>62.16</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.051963</v>
+        <v>51.963</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.059875</v>
+        <v>59.875</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.036389</v>
+        <v>36.389</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.01277</v>
+        <v>-12.77</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.269358</v>
+        <v>269.358</v>
       </c>
     </row>
     <row r="17">
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.006595</v>
+        <v>6.595</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.006436</v>
+        <v>6.436</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.004789</v>
+        <v>4.789</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.000107</v>
+        <v>0.107</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.010314</v>
+        <v>10.314</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.029353</v>
+        <v>29.353</v>
       </c>
     </row>
     <row r="18">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.055565</v>
+        <v>55.565</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.045527</v>
+        <v>45.527</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.055086</v>
+        <v>55.086</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.002456</v>
+        <v>-23.084</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.298711</v>
+        <v>240.005</v>
       </c>
     </row>
     <row r="21">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.055565</v>
+        <v>55.565</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.045527</v>
+        <v>45.527</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.055086</v>
+        <v>55.086</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.002456</v>
+        <v>-23.084</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.298711</v>
+        <v>240.005</v>
       </c>
     </row>
     <row r="24">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.11576</v>
+        <v>115.760417</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.146861</v>
+        <v>146.86129</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.157389</v>
+        <v>157.388571</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.201567</v>
+        <v>201.566667</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.022327</v>
+        <v>209.854545</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.253145</v>
+        <v>203.394068</v>
       </c>
     </row>
     <row r="27">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.06216</v>
+        <v>62.16</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.051963</v>
+        <v>51.963</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.059875</v>
+        <v>59.875</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.036389</v>
+        <v>36.389</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.01277</v>
+        <v>-12.77</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.269358</v>
+        <v>269.358</v>
       </c>
     </row>
     <row r="28">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.06216</v>
+        <v>62.16</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.051963</v>
+        <v>51.963</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.059875</v>
+        <v>59.875</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.036389</v>
+        <v>36.389</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.01277</v>
+        <v>-12.77</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.269358</v>
+        <v>269.358</v>
       </c>
     </row>
     <row r="30">
@@ -1235,10 +1235,10 @@
         <v>17.78320197623809</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-0.9130417002799349</v>
+        <v>-8.581699759471507</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>76.84793570428913</v>
+        <v>61.74492673088005</v>
       </c>
     </row>
     <row r="33">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.071284</v>
+        <v>71.28400000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.071284</v>
+        <v>71.28400000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.005814</v>
+        <v>5.814</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.009688</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.011096</v>
+        <v>11.096</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.00899</v>
+        <v>8.99</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.000284</v>
+        <v>0.284</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.003118</v>
+        <v>3.118</v>
       </c>
     </row>
     <row r="40">
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.005814</v>
+        <v>5.814</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.009688</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.011096</v>
+        <v>11.096</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.00899</v>
+        <v>8.99</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.000284</v>
+        <v>0.284</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.003118</v>
+        <v>3.118</v>
       </c>
     </row>
     <row r="42">
@@ -1583,19 +1583,19 @@
         <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.001372</v>
+        <v>1.372</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.001392</v>
+        <v>1.392</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.003835</v>
+        <v>3.835</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.004665</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="48">
@@ -1605,22 +1605,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.032121</v>
+        <v>32.121</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.020696</v>
+        <v>20.696</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.008413</v>
+        <v>8.413</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.029277</v>
+        <v>29.277</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.035281</v>
+        <v>35.281</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.07373</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="49">
@@ -1630,22 +1630,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0.058572</v>
+        <v>58.572</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.07242800000000001</v>
+        <v>72.428</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.09060699999999999</v>
+        <v>90.607</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.057038</v>
+        <v>57.038</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.075645</v>
+        <v>75.645</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.152797</v>
+        <v>152.797</v>
       </c>
     </row>
     <row r="50">
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.027577</v>
+        <v>27.577</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.013672</v>
+        <v>13.672</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.006248</v>
+        <v>6.248</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.00301</v>
+        <v>3.01</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.017421</v>
+        <v>17.421</v>
       </c>
     </row>
     <row r="51">
@@ -1942,22 +1942,22 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>1.21477</v>
+        <v>1214.77</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.217309</v>
+        <v>1217.309</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.246424</v>
+        <v>1246.424</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.831178</v>
+        <v>1831.178</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.691324</v>
+        <v>1691.324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.94326</v>
+        <v>1943.26</v>
       </c>
     </row>
     <row r="62">
@@ -1967,22 +1967,22 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>1.242347</v>
+        <v>1242.347</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1.230981</v>
+        <v>1230.981</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1.246424</v>
+        <v>1246.424</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1.837426</v>
+        <v>1837.426</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1.694334</v>
+        <v>1694.334</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.960681</v>
+        <v>1960.681</v>
       </c>
     </row>
     <row r="63">
@@ -1992,22 +1992,22 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>1.300919</v>
+        <v>1300.919</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1.303409</v>
+        <v>1303.409</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.337031</v>
+        <v>1337.031</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1.894464</v>
+        <v>1894.464</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1.769979</v>
+        <v>1769.979</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>2.113478</v>
+        <v>2113.478</v>
       </c>
     </row>
     <row r="64">
@@ -2292,22 +2292,22 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.004119</v>
+        <v>4.119</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.00447</v>
+        <v>4.47</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.012586</v>
+        <v>12.586</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.017315</v>
+        <v>17.315</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.027126</v>
+        <v>27.126</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.038947</v>
+        <v>38.947</v>
       </c>
     </row>
     <row r="76">
@@ -2317,22 +2317,22 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>0.004119</v>
+        <v>4.119</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.00447</v>
+        <v>4.47</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.012586</v>
+        <v>12.586</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.017315</v>
+        <v>17.315</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.027126</v>
+        <v>27.126</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.038947</v>
+        <v>38.947</v>
       </c>
     </row>
     <row r="77">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>0.275</v>
+        <v>275</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0.275</v>
+        <v>275</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0.002857</v>
+        <v>2.857</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.001026</v>
+        <v>1.026</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.002841</v>
+        <v>2.841</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.004014</v>
+        <v>4.014</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.002826</v>
+        <v>2.826</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.008159</v>
+        <v>8.159000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>0.277857</v>
+        <v>277.857</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.004317</v>
+        <v>4.317</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.005966</v>
+        <v>5.966</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.06640799999999999</v>
+        <v>66.408</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.007133</v>
+        <v>7.133</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.029314</v>
+        <v>29.314</v>
       </c>
     </row>
     <row r="87">
@@ -2602,22 +2602,22 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>0.281976</v>
+        <v>281.976</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>0.008787</v>
+        <v>8.787000000000001</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.018552</v>
+        <v>18.552</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>0.08372300000000001</v>
+        <v>83.723</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.034259</v>
+        <v>34.259</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.068261</v>
+        <v>68.261</v>
       </c>
     </row>
     <row r="88">
@@ -2627,22 +2627,22 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>1.009151</v>
+        <v>1009.151</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>1.253013</v>
+        <v>1253.013</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1.250194</v>
+        <v>1250.194</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>1.74918</v>
+        <v>1749.18</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>1.744341</v>
+        <v>1744.341</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>1.864823</v>
+        <v>1864.823</v>
       </c>
     </row>
     <row r="89">
@@ -2677,22 +2677,22 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>0.010035</v>
+        <v>10.035</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0.040298</v>
+        <v>40.298</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.06367</v>
+        <v>63.67</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.046831</v>
+        <v>46.831</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>-0.023773</v>
+        <v>-23.773</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.16495</v>
+        <v>164.95</v>
       </c>
     </row>
     <row r="91">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>-0.000243</v>
+        <v>-0.243</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2777,22 +2777,22 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>1.018943</v>
+        <v>1018.943</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>1.294622</v>
+        <v>1294.622</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1.318479</v>
+        <v>1318.479</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>1.810741</v>
+        <v>1810.741</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1.73572</v>
+        <v>1735.72</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>2.045217</v>
+        <v>2045.217</v>
       </c>
     </row>
     <row r="95">
@@ -2827,22 +2827,22 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>1.018943</v>
+        <v>1018.943</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>1.294622</v>
+        <v>1294.622</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>1.318479</v>
+        <v>1318.479</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1.810741</v>
+        <v>1810.741</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1.73572</v>
+        <v>1735.72</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>2.045217</v>
+        <v>2045.217</v>
       </c>
     </row>
     <row r="97">
@@ -2884,22 +2884,22 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.055565</v>
+        <v>55.565</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.045527</v>
+        <v>45.527</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.055086</v>
+        <v>55.086</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.002456</v>
+        <v>-23.084</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.298711</v>
+        <v>240.005</v>
       </c>
     </row>
     <row r="100">
@@ -3059,22 +3059,22 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.004954</v>
+        <v>-4.954</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.000775</v>
+        <v>0.775</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.0004</v>
+        <v>-0.4</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.001732</v>
+        <v>-1.732</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.000226</v>
+        <v>-0.226</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.009402000000000001</v>
+        <v>9.401999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3087,19 +3087,19 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>1.311</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.003304</v>
+        <v>3.304</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.003406</v>
+        <v>3.406</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.000422</v>
+        <v>0.422</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.000292</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="108">
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>0</v>
+        <v>7.864</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>27.107</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -3262,10 +3262,10 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.322</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-2.594</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -3287,19 +3287,19 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>6.258</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>3.083</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>2.017</v>
       </c>
     </row>
     <row r="116">
@@ -3384,22 +3384,22 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>-0.651654</v>
+        <v>-651.654</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>-0.048145</v>
+        <v>-48.145</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>-0.048916</v>
+        <v>-48.916</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.212979</v>
+        <v>-212.979</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>-0.08196000000000001</v>
+        <v>-81.95999999999999</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>-0.217971</v>
+        <v>-217.971</v>
       </c>
     </row>
     <row r="120">
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0.001758</v>
+        <v>1.758</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.000146</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="121">
@@ -3484,22 +3484,22 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0.328</v>
+        <v>328</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0.044</v>
+        <v>44</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0.13</v>
+        <v>130</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0.063</v>
+        <v>63</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0.113</v>
+        <v>113</v>
       </c>
     </row>
     <row r="124">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>-0.11</v>
+        <v>-110</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>-0.319</v>
+        <v>-319</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.073</v>
+        <v>-73</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-0.12</v>
+        <v>-120</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>-0.113</v>
+        <v>-113</v>
       </c>
     </row>
     <row r="125">
@@ -3534,19 +3534,19 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0.218</v>
+        <v>218</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-0.275</v>
+        <v>-275</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.057</v>
+        <v>57</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-0.057</v>
+        <v>-57</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -3562,19 +3562,19 @@
         <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>-0.014838</v>
+        <v>-14.838</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>-0.030406</v>
+        <v>-30.406</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.041311</v>
+        <v>-41.311</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>-0.043279</v>
+        <v>-43.279</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>-0.045845</v>
+        <v>-45.845</v>
       </c>
     </row>
     <row r="127">
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>-0.018646</v>
+        <v>-18.646</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -3646,22 +3646,22 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>0.577128</v>
+        <v>577.128</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>-0.051835</v>
+        <v>-51.835</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>-0.03875</v>
+        <v>-38.75</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.005123</v>
+        <v>5.123</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>-0.1126</v>
+        <v>-112.6</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>-0.059858</v>
+        <v>-59.858</v>
       </c>
     </row>
     <row r="130">
@@ -3671,22 +3671,22 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>0.010768</v>
+        <v>10.768</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
     </row>
     <row r="131">
@@ -3721,22 +3721,22 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>0.009868999999999999</v>
+        <v>9.869</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.020035</v>
+        <v>20.035</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.030426</v>
+        <v>30.426</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.053719</v>
+        <v>-53.719</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.018866</v>
+        <v>18.866</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>0.035039</v>
+        <v>35.039</v>
       </c>
     </row>
     <row r="133">
@@ -3746,22 +3746,22 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>0.071284</v>
+        <v>71.28400000000001</v>
       </c>
     </row>
     <row r="134">
@@ -3796,22 +3796,22 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.08437699999999999</v>
+        <v>84.377</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.120015</v>
+        <v>120.015</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.118376</v>
+        <v>118.376</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.154138</v>
+        <v>154.138</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>0.213503</v>
+        <v>213.503</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.312832</v>
+        <v>312.832</v>
       </c>
     </row>
   </sheetData>
@@ -3904,22 +3904,22 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.071284</v>
+        <v>71.28400000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.016953</v>
+        <v>16.953</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.022772</v>
+        <v>22.772</v>
       </c>
     </row>
     <row r="4">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.001372</v>
+        <v>1.372</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.001392</v>
+        <v>1.392</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.003835</v>
+        <v>3.835</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.004665</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="5">
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.014252</v>
+        <v>14.252</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.033537</v>
+        <v>33.537</v>
       </c>
     </row>
     <row r="6">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.00301</v>
+        <v>3.01</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.017421</v>
+        <v>17.421</v>
       </c>
     </row>
     <row r="7">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="5" t="n">
-        <v>0.000954</v>
+        <v>0.954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.001605</v>
+        <v>1.605</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.001066</v>
+        <v>1.066</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.000284</v>
+        <v>0.284</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.003118</v>
+        <v>3.118</v>
       </c>
     </row>
     <row r="9">
@@ -4186,22 +4186,22 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.058572</v>
+        <v>58.572</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07242800000000001</v>
+        <v>72.428</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.09060699999999999</v>
+        <v>90.607</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.057038</v>
+        <v>57.038</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.075645</v>
+        <v>75.645</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.152797</v>
+        <v>152.797</v>
       </c>
     </row>
     <row r="10">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1.646634</v>
+        <v>1646.634</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1.89447</v>
+        <v>1894.47</v>
       </c>
     </row>
     <row r="11">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.008446</v>
+        <v>8.446</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.00587</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="12">
@@ -4312,16 +4312,16 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.004547</v>
+        <v>4.547</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.003495</v>
+        <v>3.495</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.002467</v>
+        <v>2.467</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.002863</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="13">
@@ -4347,19 +4347,19 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1.230981</v>
+        <v>1230.981</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.246424</v>
+        <v>1246.424</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1.837426</v>
+        <v>1837.426</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1.694334</v>
+        <v>1694.334</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1.960681</v>
+        <v>1960.681</v>
       </c>
     </row>
     <row r="14">
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1.300919</v>
+        <v>1300.919</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1.303409</v>
+        <v>1303.409</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.337031</v>
+        <v>1337.031</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>1.894464</v>
+        <v>1894.464</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1.769979</v>
+        <v>1769.979</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2.113478</v>
+        <v>2113.478</v>
       </c>
     </row>
     <row r="15">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.02309</v>
+        <v>23.09</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.035073</v>
+        <v>35.073</v>
       </c>
     </row>
     <row r="16">
@@ -4460,22 +4460,22 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.000538</v>
+        <v>0.538</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.000334</v>
+        <v>0.334</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0009890000000000001</v>
+        <v>0.989</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.001259</v>
+        <v>1.259</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.003718</v>
+        <v>3.718</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.003495</v>
+        <v>3.495</v>
       </c>
     </row>
     <row r="17">
@@ -4502,16 +4502,16 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.000277</v>
+        <v>0.277</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.00039</v>
+        <v>0.39</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.000318</v>
+        <v>0.318</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.000379</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="18">
@@ -4532,22 +4532,22 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.004119</v>
+        <v>4.119</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.00447</v>
+        <v>4.47</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.012586</v>
+        <v>12.586</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.017315</v>
+        <v>17.315</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.027126</v>
+        <v>27.126</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.038947</v>
+        <v>38.947</v>
       </c>
     </row>
     <row r="19">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.002826</v>
+        <v>2.826</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.008159</v>
+        <v>8.159000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -4612,22 +4612,22 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.277857</v>
+        <v>277.857</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.004317</v>
+        <v>4.317</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.005966</v>
+        <v>5.966</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.06640799999999999</v>
+        <v>66.408</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.007133</v>
+        <v>7.133</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.029314</v>
+        <v>29.314</v>
       </c>
     </row>
     <row r="21">
@@ -4662,16 +4662,16 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.250194</v>
+        <v>1250.194</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1.74918</v>
+        <v>1749.18</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1.744341</v>
+        <v>1744.341</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1.864823</v>
+        <v>1864.823</v>
       </c>
     </row>
     <row r="22">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.023773</v>
+        <v>-23.773</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.16495</v>
+        <v>164.95</v>
       </c>
     </row>
     <row r="23">
@@ -4745,19 +4745,19 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.001311</v>
+        <v>1.311</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.004615</v>
+        <v>4.615</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.01473</v>
+        <v>14.73</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.015152</v>
+        <v>15.152</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.015444</v>
+        <v>15.444</v>
       </c>
     </row>
     <row r="24">
@@ -4787,19 +4787,19 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.294622</v>
+        <v>1294.622</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.318479</v>
+        <v>1318.479</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>1.810741</v>
+        <v>1810.741</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>1.73572</v>
+        <v>1735.72</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>2.045217</v>
+        <v>2045.217</v>
       </c>
     </row>
     <row r="25">
@@ -4829,19 +4829,19 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.303409</v>
+        <v>1303.409</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.337031</v>
+        <v>1337.031</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1.894464</v>
+        <v>1894.464</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1.769979</v>
+        <v>1769.979</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>2.113478</v>
+        <v>2113.478</v>
       </c>
     </row>
     <row r="26">
@@ -4872,13 +4872,13 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.009603</v>
+        <v>9.603</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.013725</v>
+        <v>13.725</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.016953</v>
+        <v>16.953</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.007699</v>
+        <v>7.699</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.014252</v>
+        <v>14.252</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.006248</v>
+        <v>6.248</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.00301</v>
+        <v>3.01</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -4988,19 +4988,19 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.005814</v>
+        <v>5.814</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.009688</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.011096</v>
+        <v>11.096</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.00899</v>
+        <v>8.99</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.000284</v>
+        <v>0.284</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5022,19 +5022,19 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>1.22872</v>
+        <v>1228.72</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1.225233</v>
+        <v>1225.233</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.228171</v>
+        <v>1228.171</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>1.773053</v>
+        <v>1773.053</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>1.646634</v>
+        <v>1646.634</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.009343000000000001</v>
+        <v>9.343</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.008446</v>
+        <v>8.446</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.01132</v>
+        <v>11.32</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.015666</v>
+        <v>15.666</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.02309</v>
+        <v>23.09</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.057</v>
+        <v>57</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -5189,16 +5189,16 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.001026</v>
+        <v>1.026</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.002841</v>
+        <v>2.841</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.004014</v>
+        <v>4.014</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.002826</v>
+        <v>2.826</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.046831</v>
+        <v>46.831</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.023773</v>
+        <v>-23.773</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.009906</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.013947</v>
+        <v>13.947</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.00261</v>
+        <v>2.61</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.009343000000000001</v>
+        <v>9.343</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.032549</v>
+        <v>32.549</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.040298</v>
+        <v>40.298</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.06367</v>
+        <v>63.67</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.046831</v>
+        <v>46.831</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>0.009403999999999999</v>
+        <v>9.404</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.007024</v>
+        <v>7.024</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.009603</v>
+        <v>9.603</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.013672</v>
+        <v>13.672</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.009906</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5522,13 +5522,13 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.005819</v>
+        <v>5.819</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.003151</v>
+        <v>3.151</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.004547</v>
+        <v>4.547</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5560,13 +5560,13 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.001994</v>
+        <v>1.994</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.002597</v>
+        <v>2.597</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.00261</v>
+        <v>2.61</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.003329</v>
+        <v>3.329</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.003866</v>
+        <v>3.866</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.01132</v>
+        <v>11.32</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.00027</v>
+        <v>0.27</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.000277</v>
+        <v>0.277</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.000857</v>
+        <v>0.857</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.00164</v>
+        <v>1.64</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1.253013</v>
+        <v>1253.013</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.250194</v>
+        <v>1250.194</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.027577</v>
+        <v>27.577</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.013672</v>
+        <v>13.672</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1.242347</v>
+        <v>1242.347</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1.230981</v>
+        <v>1230.981</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5856,10 +5856,10 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>0.000252</v>
+        <v>0.252</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.00027</v>
+        <v>0.27</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.275</v>
+        <v>275</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.001126</v>
+        <v>1.126</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.000857</v>
+        <v>0.857</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>0.000331</v>
+        <v>0.331</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1.009151</v>
+        <v>1009.151</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>1.253013</v>
+        <v>1253.013</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.010035</v>
+        <v>10.035</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.040298</v>
+        <v>40.298</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>-0.000243</v>
+        <v>-0.243</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.001311</v>
+        <v>1.311</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1.018943</v>
+        <v>1018.943</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>1.294622</v>
+        <v>1294.622</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1.300919</v>
+        <v>1300.919</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>1.303409</v>
+        <v>1303.409</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>-0.023084</v>
+        <v>-23.084</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0.240005</v>
+        <v>240.005</v>
       </c>
     </row>
     <row r="61">
@@ -6374,16 +6374,16 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.050085</v>
+        <v>50.085</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.065108</v>
+        <v>65.108</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>0.075554</v>
+        <v>75.554</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>0.07925500000000001</v>
+        <v>79.255</v>
       </c>
     </row>
     <row r="62">
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0.016919</v>
+        <v>16.919</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0.019149</v>
+        <v>19.149</v>
       </c>
     </row>
     <row r="63">
@@ -6467,13 +6467,13 @@
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.000369</v>
+        <v>0.369</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>0.000346</v>
+        <v>0.346</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>0.000323</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="64">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0.148034</v>
+        <v>148.034</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="65">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="J65" s="5" t="n">
-        <v>-0.00671</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="66">
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="I66" s="5" t="n">
-        <v>-0.012775</v>
+        <v>-12.775</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.046233</v>
+        <v>-46.233</v>
       </c>
     </row>
     <row r="67">
@@ -6642,16 +6642,16 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.003304</v>
+        <v>3.304</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.003406</v>
+        <v>3.406</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0.000422</v>
+        <v>0.422</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>0.000292</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="68">
@@ -6672,10 +6672,10 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>0.006595</v>
+        <v>6.595</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.006436</v>
+        <v>6.436</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="I68" s="5" t="n">
-        <v>0.010314</v>
+        <v>10.314</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>0.029353</v>
+        <v>29.353</v>
       </c>
     </row>
     <row r="69">
@@ -6722,16 +6722,16 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.003766</v>
+        <v>3.766</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.004348</v>
+        <v>4.348</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.004991</v>
+        <v>4.991</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>0.003873</v>
+        <v>3.873</v>
       </c>
     </row>
     <row r="70">
@@ -6752,22 +6752,22 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>0.09667100000000001</v>
+        <v>96.67100000000001</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.124543</v>
+        <v>124.543</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.123807</v>
+        <v>123.807</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.161953</v>
+        <v>161.953</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0.220721</v>
+        <v>220.721</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>0.315007</v>
+        <v>315.007</v>
       </c>
     </row>
     <row r="71">
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>-0.006083</v>
+        <v>-6.083</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>-0.006992</v>
+        <v>-6.992</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>-0.011577</v>
+        <v>-11.577</v>
       </c>
     </row>
     <row r="72">
@@ -6844,16 +6844,16 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.4</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.001732</v>
+        <v>-1.732</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>-0.000226</v>
+        <v>-0.226</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>0.009402000000000001</v>
+        <v>9.401999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -6878,22 +6878,22 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0.08437699999999999</v>
+        <v>84.377</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.120015</v>
+        <v>120.015</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.118376</v>
+        <v>118.376</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.154138</v>
+        <v>154.138</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.213503</v>
+        <v>213.503</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.312832</v>
+        <v>312.832</v>
       </c>
     </row>
     <row r="74">
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.057489</v>
+        <v>-57.489</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.218619</v>
+        <v>-218.619</v>
       </c>
     </row>
     <row r="75">
@@ -6973,13 +6973,13 @@
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.0017</v>
+        <v>1.7</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>0.000366</v>
+        <v>0.366</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>0.002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -6998,17 +6998,21 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.00344</v>
+        <v>3.44</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.006258</v>
+        <v>6.258</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -7016,10 +7020,10 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.003083</v>
+        <v>3.083</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0.002017</v>
+        <v>2.017</v>
       </c>
     </row>
     <row r="77">
@@ -7060,10 +7064,10 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.014639</v>
+        <v>-14.639</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.0043</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="78">
@@ -7104,10 +7108,10 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>-0.013281</v>
+        <v>-13.281</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>-0.007669</v>
+        <v>-7.669</v>
       </c>
     </row>
     <row r="79">
@@ -7132,22 +7136,22 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>-0.651654</v>
+        <v>-651.654</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.048145</v>
+        <v>-48.145</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.048916</v>
+        <v>-48.916</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>-0.212979</v>
+        <v>-212.979</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.08196000000000001</v>
+        <v>-81.95999999999999</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.217971</v>
+        <v>-217.971</v>
       </c>
     </row>
     <row r="80">
@@ -7192,10 +7196,10 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.063</v>
+        <v>63</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>0.113</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81">
@@ -7240,10 +7244,10 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>-0.12</v>
+        <v>-120</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.113</v>
+        <v>-113</v>
       </c>
     </row>
     <row r="82">
@@ -7288,10 +7292,10 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>0.001758</v>
+        <v>1.758</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>0.000146</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="83">
@@ -7332,10 +7336,10 @@
         </is>
       </c>
       <c r="I83" s="5" t="n">
-        <v>-0.008917</v>
+        <v>-8.917</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.009013</v>
+        <v>-9.013</v>
       </c>
     </row>
     <row r="84">
@@ -7370,16 +7374,16 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.030406</v>
+        <v>-30.406</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>-0.041311</v>
+        <v>-41.311</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>-0.043279</v>
+        <v>-43.279</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>-0.045845</v>
+        <v>-45.845</v>
       </c>
     </row>
     <row r="85">
@@ -7405,19 +7409,19 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-0.000339</v>
+        <v>-0.339</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.000359</v>
+        <v>-0.359</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>-0.000436</v>
+        <v>-0.436</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>-0.000431</v>
+        <v>-0.431</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>-0.000457</v>
+        <v>-0.457</v>
       </c>
     </row>
     <row r="86">
@@ -7458,10 +7462,10 @@
         </is>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.004731</v>
+        <v>-4.731</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.003056</v>
+        <v>-3.056</v>
       </c>
     </row>
     <row r="87">
@@ -7507,7 +7511,7 @@
         </is>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.001633</v>
+        <v>-1.633</v>
       </c>
     </row>
     <row r="88">
@@ -7537,10 +7541,10 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.051835</v>
+        <v>-51.835</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.03875</v>
+        <v>-38.75</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7548,10 +7552,10 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>-0.1126</v>
+        <v>-112.6</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.059858</v>
+        <v>-59.858</v>
       </c>
     </row>
     <row r="89">
@@ -7582,16 +7586,16 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.000284</v>
+        <v>-0.284</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>-1e-06</v>
+        <v>-0.001</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>-7.7e-05</v>
+        <v>-0.077</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>3.6e-05</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="90">
@@ -7612,10 +7616,10 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
-        <v>0.009868999999999999</v>
+        <v>9.869</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.020035</v>
+        <v>20.035</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7628,10 +7632,10 @@
         </is>
       </c>
       <c r="I90" s="5" t="n">
-        <v>0.018866</v>
+        <v>18.866</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>0.035039</v>
+        <v>35.039</v>
       </c>
     </row>
     <row r="91">
@@ -7656,22 +7660,22 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.010768</v>
+        <v>10.768</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
     </row>
     <row r="92">
@@ -7696,22 +7700,22 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.017379</v>
+        <v>17.379</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.036245</v>
+        <v>36.245</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>0.071284</v>
+        <v>71.28400000000001</v>
       </c>
     </row>
     <row r="93">
@@ -7747,10 +7751,10 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.023084</v>
+        <v>-23.084</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -7791,10 +7795,10 @@
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0.015972</v>
+        <v>15.972</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.016919</v>
+        <v>16.919</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -7835,10 +7839,10 @@
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.03683</v>
+        <v>36.83</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.148034</v>
+        <v>148.034</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -7879,7 +7883,7 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7925,10 +7929,10 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>-0.001467</v>
+        <v>-1.467</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.012775</v>
+        <v>-12.775</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -7964,13 +7968,13 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.004789</v>
+        <v>4.789</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.000107</v>
+        <v>0.107</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.010314</v>
+        <v>10.314</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -8011,10 +8015,10 @@
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.004346</v>
+        <v>4.346</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.004991</v>
+        <v>4.991</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -8055,10 +8059,10 @@
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.190895</v>
+        <v>-190.895</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.057489</v>
+        <v>-57.489</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -8099,10 +8103,10 @@
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.021043</v>
+        <v>-21.043</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.014639</v>
+        <v>-14.639</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -8143,10 +8147,10 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.002741</v>
+        <v>-2.741</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.013281</v>
+        <v>-13.281</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -8191,10 +8195,10 @@
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.13</v>
+        <v>130</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.063</v>
+        <v>63</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -8239,10 +8243,10 @@
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.073</v>
+        <v>-73</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>-0.12</v>
+        <v>-120</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -8283,10 +8287,10 @@
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.016837</v>
+        <v>16.837</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0.001758</v>
+        <v>1.758</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -8327,10 +8331,10 @@
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>-0.020713</v>
+        <v>-20.713</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>-0.008917</v>
+        <v>-8.917</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -8371,10 +8375,10 @@
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>-0.006254</v>
+        <v>-6.254</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>-0.004731</v>
+        <v>-4.731</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -8419,10 +8423,10 @@
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.005123</v>
+        <v>5.123</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-0.1126</v>
+        <v>-112.6</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -8463,10 +8467,10 @@
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-0.053719</v>
+        <v>-53.719</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.018866</v>
+        <v>18.866</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -8496,16 +8500,16 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.055565</v>
+        <v>55.565</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.045527</v>
+        <v>45.527</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.055086</v>
+        <v>55.086</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -8546,10 +8550,10 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.000836</v>
+        <v>0.836</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.015972</v>
+        <v>15.972</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -8594,10 +8598,10 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.000374</v>
+        <v>0.374</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.000369</v>
+        <v>0.369</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -8626,7 +8630,11 @@
           <t>Impairment charges (Note 12)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -8638,10 +8646,10 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.0036</v>
+        <v>3.6</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.027107</v>
+        <v>27.107</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -8687,7 +8695,7 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.009723000000000001</v>
+        <v>9.723000000000001</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -8728,10 +8736,10 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>-0.002099</v>
+        <v>-2.099</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -8772,10 +8780,10 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.004066</v>
+        <v>4.066</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>-0.001469</v>
+        <v>-1.469</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -8810,16 +8818,16 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>-0.00734</v>
+        <v>-7.34</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>-0.005303</v>
+        <v>-5.303</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>-0.005031</v>
+        <v>-5.031</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>-0.006083</v>
+        <v>-6.083</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -8860,10 +8868,10 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>-0.05228</v>
+        <v>-52.28</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>-0.190895</v>
+        <v>-190.895</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -8904,10 +8912,10 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.0045</v>
+        <v>4.5</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0.0017</v>
+        <v>1.7</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -8953,7 +8961,7 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>-0.021043</v>
+        <v>-21.043</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -8994,10 +9002,10 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-0.007394</v>
+        <v>-7.394</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-0.002741</v>
+        <v>-2.741</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -9038,10 +9046,10 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>-0.004127</v>
+        <v>-4.127</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>-0.020713</v>
+        <v>-20.713</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -9082,10 +9090,10 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>-0.000359</v>
+        <v>-0.359</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>-0.000436</v>
+        <v>-0.436</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -9126,10 +9134,10 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>-0.002014</v>
+        <v>-2.014</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>-0.006254</v>
+        <v>-6.254</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -9160,7 +9168,7 @@
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="n">
-        <v>-0.000844</v>
+        <v>-0.844</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9168,7 +9176,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>-0.001844</v>
+        <v>-1.844</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -9218,10 +9226,10 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>-0.03875</v>
+        <v>-38.75</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>0.005123</v>
+        <v>5.123</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -9262,10 +9270,10 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.030426</v>
+        <v>30.426</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>-0.053719</v>
+        <v>-53.719</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -9296,13 +9304,13 @@
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" s="5" t="n">
-        <v>0.053231</v>
+        <v>53.231</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.053672</v>
+        <v>53.672</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.050085</v>
+        <v>50.085</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -9348,7 +9356,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.000836</v>
+        <v>0.836</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -9388,13 +9396,13 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.000399</v>
+        <v>0.399</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.000399</v>
+        <v>0.399</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.000374</v>
+        <v>0.374</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -9428,9 +9436,13 @@
           <t>Impairment charges (Note 13)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
-        <v>0.007863999999999999</v>
+        <v>7.864</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -9438,7 +9450,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.0036</v>
+        <v>3.6</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -9484,7 +9496,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>-0.002099</v>
+        <v>-2.099</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -9525,10 +9537,10 @@
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.010786</v>
+        <v>10.786</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.004066</v>
+        <v>4.066</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -9562,17 +9574,21 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.001311</v>
+        <v>1.311</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.003304</v>
+        <v>3.304</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -9613,10 +9629,10 @@
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.006436</v>
+        <v>6.436</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.004789</v>
+        <v>4.789</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -9652,13 +9668,13 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" s="5" t="n">
-        <v>0.01039</v>
+        <v>10.39</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.006412</v>
+        <v>6.412</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.003766</v>
+        <v>3.766</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -9698,13 +9714,13 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>-0.004954</v>
+        <v>-4.954</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.000775</v>
+        <v>0.775</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.4</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -9740,13 +9756,13 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" s="5" t="n">
-        <v>-0.7296820000000001</v>
+        <v>-729.682</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>-0.051263</v>
+        <v>-51.263</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>-0.05228</v>
+        <v>-52.28</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9792,7 +9808,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.0045</v>
+        <v>4.5</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9826,17 +9842,21 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
-        <v>-0.000322</v>
+        <v>-0.322</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>-0.002594</v>
+        <v>-2.594</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9882,7 +9902,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-4.8</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9927,7 +9947,7 @@
         </is>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.044</v>
+        <v>44</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -9977,7 +9997,7 @@
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>-0.319</v>
+        <v>-319</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -10016,14 +10036,18 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.245115</v>
+        <v>245.115</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -10069,10 +10093,10 @@
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>-0.001679</v>
+        <v>-1.679</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>-0.004127</v>
+        <v>-4.127</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -10117,10 +10141,10 @@
         </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.014838</v>
+        <v>-14.838</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>-0.030406</v>
+        <v>-30.406</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -10161,10 +10185,10 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-0.005094</v>
+        <v>-5.094</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>-0.002014</v>
+        <v>-2.014</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -10205,10 +10229,10 @@
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.020035</v>
+        <v>20.035</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.030426</v>
+        <v>30.426</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -10253,10 +10277,10 @@
         </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.020637</v>
+        <v>20.637</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -10301,10 +10325,10 @@
         </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.040672</v>
+        <v>40.672</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.07109799999999999</v>
+        <v>71.098</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -10340,10 +10364,10 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" s="5" t="n">
-        <v>-0.006447</v>
+        <v>-6.447</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.010786</v>
+        <v>10.786</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -10384,7 +10408,7 @@
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" s="5" t="n">
-        <v>0.078028</v>
+        <v>78.02800000000001</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -10435,7 +10459,7 @@
         </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>0.003118</v>
+        <v>3.118</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -10480,10 +10504,10 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.328</v>
+        <v>328</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.044</v>
+        <v>44</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -10528,10 +10552,10 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>-0.11</v>
+        <v>-110</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>-0.319</v>
+        <v>-319</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -10570,12 +10594,16 @@
           <t>Proceeds from share issuance (Note 24)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
-        <v>0.37</v>
+        <v>370</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.263761</v>
+        <v>263.761</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -10625,7 +10653,7 @@
         </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>-0.018646</v>
+        <v>-18.646</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -10666,10 +10694,10 @@
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" s="5" t="n">
-        <v>-0.000218</v>
+        <v>-0.218</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.000258</v>
+        <v>-0.258</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -10710,10 +10738,10 @@
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" s="5" t="n">
-        <v>-8.899999999999999e-05</v>
+        <v>-0.089</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-8.1e-05</v>
+        <v>-0.081</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -10754,10 +10782,10 @@
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" s="5" t="n">
-        <v>-0.009721</v>
+        <v>-9.721</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.005094</v>
+        <v>-5.094</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -10802,10 +10830,10 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0.577128</v>
+        <v>577.128</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>0.051835</v>
+        <v>51.835</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -10856,16 +10884,16 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.151885</v>
+        <v>151.885</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>0.204024</v>
+        <v>204.024</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>0.268991</v>
+        <v>268.991</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>0.388704</v>
+        <v>388.704</v>
       </c>
     </row>
     <row r="163">
@@ -10891,19 +10919,19 @@
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0.013496</v>
+        <v>13.496</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.014796</v>
+        <v>14.796</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>-0.03684</v>
+        <v>-36.84</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>-0.038227</v>
+        <v>-38.227</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>-0.046531</v>
+        <v>-46.531</v>
       </c>
     </row>
     <row r="164">
@@ -10933,19 +10961,19 @@
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.053672</v>
+        <v>53.672</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.050085</v>
+        <v>50.085</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>-0.065108</v>
+        <v>-65.108</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>-0.075554</v>
+        <v>-75.554</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>-0.07925500000000001</v>
+        <v>-79.255</v>
       </c>
     </row>
     <row r="165">
@@ -10975,19 +11003,19 @@
         </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>0.08325299999999999</v>
+        <v>83.253</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.087004</v>
+        <v>87.004</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>0.102076</v>
+        <v>102.076</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>0.15521</v>
+        <v>155.21</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>0.262918</v>
+        <v>262.918</v>
       </c>
     </row>
     <row r="166">
@@ -11028,10 +11056,10 @@
         </is>
       </c>
       <c r="I166" s="5" t="n">
-        <v>-0.021755</v>
+        <v>-21.755</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>-0.030452</v>
+        <v>-30.452</v>
       </c>
     </row>
     <row r="167">
@@ -11072,10 +11100,10 @@
         </is>
       </c>
       <c r="I167" s="5" t="n">
-        <v>-0.003405</v>
+        <v>-3.405</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>-0.005648</v>
+        <v>-5.648</v>
       </c>
     </row>
     <row r="168">
@@ -11116,10 +11144,10 @@
         </is>
       </c>
       <c r="I168" s="5" t="n">
-        <v>-0.148034</v>
+        <v>-148.034</v>
       </c>
       <c r="J168" s="5" t="n">
-        <v>0.0043</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="169">
@@ -11169,7 +11197,7 @@
         </is>
       </c>
       <c r="J169" s="5" t="n">
-        <v>-0.010299</v>
+        <v>-10.299</v>
       </c>
     </row>
     <row r="170">
@@ -11214,10 +11242,10 @@
         </is>
       </c>
       <c r="I170" s="5" t="n">
-        <v>-0.017984</v>
+        <v>-17.984</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>0.220819</v>
+        <v>220.819</v>
       </c>
     </row>
     <row r="171">
@@ -11258,10 +11286,10 @@
         </is>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0.012775</v>
+        <v>12.775</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>0.046233</v>
+        <v>46.233</v>
       </c>
     </row>
     <row r="172">
@@ -11307,7 +11335,7 @@
         </is>
       </c>
       <c r="J172" s="5" t="n">
-        <v>0.00671</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="173">
@@ -11348,10 +11376,10 @@
         </is>
       </c>
       <c r="I173" s="5" t="n">
-        <v>-0.005073</v>
+        <v>-5.073</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>-0.003459</v>
+        <v>-3.459</v>
       </c>
     </row>
     <row r="174">
@@ -11377,19 +11405,19 @@
         </is>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.000855</v>
+        <v>0.855</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.0008050000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="H174" s="5" t="n">
-        <v>-0.00067</v>
+        <v>-0.67</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>-0.000903</v>
+        <v>-0.903</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>-0.000531</v>
+        <v>-0.531</v>
       </c>
     </row>
     <row r="175">
@@ -11430,10 +11458,10 @@
         </is>
       </c>
       <c r="I175" s="5" t="n">
-        <v>0.000181</v>
+        <v>0.181</v>
       </c>
       <c r="J175" s="5" t="n">
-        <v>-0.000414</v>
+        <v>-0.414</v>
       </c>
     </row>
     <row r="176">
@@ -11468,13 +11496,13 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.5</v>
       </c>
       <c r="H176" s="5" t="n">
-        <v>-0.003873</v>
+        <v>-3.873</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>-0.001766</v>
+        <v>-1.766</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -11524,10 +11552,10 @@
         </is>
       </c>
       <c r="I177" s="5" t="n">
-        <v>0.005214</v>
+        <v>5.214</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>0.048539</v>
+        <v>48.539</v>
       </c>
     </row>
     <row r="178">
@@ -11572,10 +11600,10 @@
         </is>
       </c>
       <c r="I178" s="5" t="n">
-        <v>-0.01277</v>
+        <v>-12.77</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>0.269358</v>
+        <v>269.358</v>
       </c>
     </row>
     <row r="179">
@@ -11620,10 +11648,10 @@
         </is>
       </c>
       <c r="I179" s="5" t="n">
-        <v>-0.010314</v>
+        <v>-10.314</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>-0.029353</v>
+        <v>-29.353</v>
       </c>
     </row>
     <row r="180">
@@ -11642,7 +11670,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -11664,10 +11696,10 @@
         </is>
       </c>
       <c r="I180" s="5" t="n">
-        <v>-0.023084</v>
+        <v>-23.084</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>0.240005</v>
+        <v>240.005</v>
       </c>
     </row>
     <row r="181">
@@ -11782,7 +11814,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -11804,10 +11840,10 @@
         </is>
       </c>
       <c r="I183" s="5" t="n">
-        <v>-0.023084</v>
+        <v>-23.084</v>
       </c>
       <c r="J183" s="5" t="n">
-        <v>0.240005</v>
+        <v>240.005</v>
       </c>
     </row>
     <row r="184">
@@ -11853,7 +11889,7 @@
         </is>
       </c>
       <c r="J184" s="5" t="n">
-        <v>0.001493</v>
+        <v>1.493</v>
       </c>
     </row>
     <row r="185">
@@ -11899,7 +11935,7 @@
         </is>
       </c>
       <c r="J185" s="5" t="n">
-        <v>-0.000396</v>
+        <v>-0.396</v>
       </c>
     </row>
     <row r="186">
@@ -11945,7 +11981,7 @@
         </is>
       </c>
       <c r="J186" s="5" t="n">
-        <v>0.001097</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="187">
@@ -11986,10 +12022,10 @@
         </is>
       </c>
       <c r="I187" s="5" t="n">
-        <v>-0.023084</v>
+        <v>-23.084</v>
       </c>
       <c r="J187" s="5" t="n">
-        <v>0.241102</v>
+        <v>241.102</v>
       </c>
     </row>
     <row r="188">
@@ -12020,13 +12056,13 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.015516</v>
+        <v>15.516</v>
       </c>
       <c r="H188" s="5" t="n">
-        <v>-0.020095</v>
+        <v>-20.095</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>-0.021755</v>
+        <v>-21.755</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -12062,13 +12098,13 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.002976</v>
+        <v>2.976</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>-0.004219</v>
+        <v>-4.219</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>-0.003405</v>
+        <v>-3.405</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -12109,10 +12145,10 @@
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>-0.03683</v>
+        <v>-36.83</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>-0.148034</v>
+        <v>-148.034</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -12153,10 +12189,10 @@
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>0.040932</v>
+        <v>40.932</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>-0.017984</v>
+        <v>-17.984</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -12197,7 +12233,7 @@
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>-0.001</v>
+        <v>-1</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -12243,10 +12279,10 @@
         </is>
       </c>
       <c r="H193" s="5" t="n">
-        <v>0.001467</v>
+        <v>1.467</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>0.012775</v>
+        <v>12.775</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -12282,13 +12318,13 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>-0.001413</v>
+        <v>-1.413</v>
       </c>
       <c r="H194" s="5" t="n">
-        <v>-0.004122</v>
+        <v>-4.122</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>-0.005073</v>
+        <v>-5.073</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -12329,10 +12365,10 @@
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>-0.000218</v>
+        <v>-0.218</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>0.000181</v>
+        <v>0.181</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -12377,10 +12413,10 @@
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>-0.004543</v>
+        <v>-4.543</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>0.005214</v>
+        <v>5.214</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -12425,10 +12461,10 @@
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>0.036389</v>
+        <v>36.389</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>-0.01277</v>
+        <v>-12.77</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -12468,13 +12504,13 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>-0.004789</v>
+        <v>-4.789</v>
       </c>
       <c r="H198" s="5" t="n">
-        <v>-0.000107</v>
+        <v>-0.107</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>-0.010314</v>
+        <v>-10.314</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -12515,10 +12551,10 @@
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>-0.023084</v>
+        <v>-23.084</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -12559,10 +12595,10 @@
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>1.8e-07</v>
+        <v>0.00018</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>-0.00011</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -12603,10 +12639,10 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>1.8e-07</v>
+        <v>0.00018</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>-0.00011</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -12642,10 +12678,10 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>0.0036</v>
+        <v>3.6</v>
       </c>
       <c r="H202" s="5" t="n">
-        <v>0.027107</v>
+        <v>27.107</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -12691,7 +12727,7 @@
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>0.009723000000000001</v>
+        <v>9.723000000000001</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12731,13 +12767,13 @@
         </is>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.068744</v>
+        <v>68.744</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>0.064107</v>
+        <v>64.107</v>
       </c>
       <c r="H204" s="5" t="n">
-        <v>0.040262</v>
+        <v>40.262</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12778,10 +12814,10 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>0.002099</v>
+        <v>2.099</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>-0.001</v>
+        <v>-1</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -12822,10 +12858,10 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>-0.004066</v>
+        <v>-4.066</v>
       </c>
       <c r="H206" s="5" t="n">
-        <v>0.001467</v>
+        <v>1.467</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -12861,13 +12897,13 @@
         </is>
       </c>
       <c r="F207" s="5" t="n">
-        <v>-2.5e-05</v>
+        <v>-0.025</v>
       </c>
       <c r="G207" s="5" t="n">
-        <v>-0.000352</v>
+        <v>-0.352</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>-0.000218</v>
+        <v>-0.218</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -12907,13 +12943,13 @@
         </is>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.051963</v>
+        <v>51.963</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>0.059875</v>
+        <v>59.875</v>
       </c>
       <c r="H208" s="5" t="n">
-        <v>0.036389</v>
+        <v>36.389</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -12953,13 +12989,13 @@
         </is>
       </c>
       <c r="F209" s="5" t="n">
-        <v>0.045527</v>
+        <v>45.527</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>0.055086</v>
+        <v>55.086</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>0.036282</v>
+        <v>36.282</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -13082,13 +13118,13 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.112588</v>
+        <v>112.588</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.150421</v>
+        <v>150.421</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>0.151885</v>
+        <v>151.885</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -13129,10 +13165,10 @@
         </is>
       </c>
       <c r="F213" s="5" t="n">
-        <v>0.012213</v>
+        <v>12.213</v>
       </c>
       <c r="G213" s="5" t="n">
-        <v>0.015516</v>
+        <v>15.516</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -13173,10 +13209,10 @@
         </is>
       </c>
       <c r="F214" s="5" t="n">
-        <v>0.000771</v>
+        <v>0.771</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>0.002976</v>
+        <v>2.976</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -13217,7 +13253,7 @@
         </is>
       </c>
       <c r="F215" s="5" t="n">
-        <v>0.00067</v>
+        <v>0.67</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -13268,7 +13304,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>0.002099</v>
+        <v>2.099</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -13309,10 +13345,10 @@
         </is>
       </c>
       <c r="F217" s="5" t="n">
-        <v>-0.010786</v>
+        <v>-10.786</v>
       </c>
       <c r="G217" s="5" t="n">
-        <v>-0.004066</v>
+        <v>-4.066</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -13353,10 +13389,10 @@
         </is>
       </c>
       <c r="F218" s="5" t="n">
-        <v>-0.005673</v>
+        <v>-5.673</v>
       </c>
       <c r="G218" s="5" t="n">
-        <v>-0.001413</v>
+        <v>-1.413</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -13406,7 +13442,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.5</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -13447,7 +13483,7 @@
         </is>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-0.000297</v>
+        <v>-0.297</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -13493,10 +13529,10 @@
         </is>
       </c>
       <c r="F221" s="5" t="n">
-        <v>-0.016781</v>
+        <v>-16.781</v>
       </c>
       <c r="G221" s="5" t="n">
-        <v>-0.004232</v>
+        <v>-4.232</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -13541,10 +13577,10 @@
         </is>
       </c>
       <c r="F222" s="5" t="n">
-        <v>-0.006436</v>
+        <v>-6.436</v>
       </c>
       <c r="G222" s="5" t="n">
-        <v>-0.004789</v>
+        <v>-4.789</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -13584,10 +13620,10 @@
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>0.053231</v>
+        <v>53.231</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>0.053672</v>
+        <v>53.672</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -13632,10 +13668,10 @@
         </is>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.050098</v>
+        <v>50.098</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.08325299999999999</v>
+        <v>83.253</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -13676,10 +13712,10 @@
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" s="5" t="n">
-        <v>0.007394</v>
+        <v>7.394</v>
       </c>
       <c r="F225" s="5" t="n">
-        <v>0.012213</v>
+        <v>12.213</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -13725,7 +13761,7 @@
         </is>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.00067</v>
+        <v>0.67</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -13766,10 +13802,10 @@
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" s="5" t="n">
-        <v>5.8e-05</v>
+        <v>0.058</v>
       </c>
       <c r="F227" s="5" t="n">
-        <v>0.000855</v>
+        <v>0.855</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -13810,10 +13846,10 @@
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" s="5" t="n">
-        <v>0.000119</v>
+        <v>0.119</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>0.000771</v>
+        <v>0.771</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -13854,7 +13890,7 @@
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" s="5" t="n">
-        <v>0.007863999999999999</v>
+        <v>7.864</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -13904,10 +13940,10 @@
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.034663</v>
+        <v>34.663</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>0.068744</v>
+        <v>68.744</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -13948,7 +13984,7 @@
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" s="5" t="n">
-        <v>0.030926</v>
+        <v>30.926</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -13994,10 +14030,10 @@
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" s="5" t="n">
-        <v>0.006447</v>
+        <v>6.447</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.010786</v>
+        <v>-10.786</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -14038,10 +14074,10 @@
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" s="5" t="n">
-        <v>-0.009860000000000001</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="F233" s="5" t="n">
-        <v>-0.005673</v>
+        <v>-5.673</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -14087,7 +14123,7 @@
         </is>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.000297</v>
+        <v>-0.297</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -14128,10 +14164,10 @@
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" s="5" t="n">
-        <v>-1.6e-05</v>
+        <v>-0.016</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>-2.5e-05</v>
+        <v>-0.025</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -14172,10 +14208,10 @@
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" s="5" t="n">
-        <v>0.027497</v>
+        <v>27.497</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.016781</v>
+        <v>-16.781</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -14220,10 +14256,10 @@
         </is>
       </c>
       <c r="E237" s="5" t="n">
-        <v>0.06216</v>
+        <v>62.16</v>
       </c>
       <c r="F237" s="5" t="n">
-        <v>0.051963</v>
+        <v>51.963</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -14268,10 +14304,10 @@
         </is>
       </c>
       <c r="E238" s="5" t="n">
-        <v>-0.006595</v>
+        <v>-6.595</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>-0.006436</v>
+        <v>-6.436</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -14316,10 +14352,10 @@
         </is>
       </c>
       <c r="E239" s="5" t="n">
-        <v>0.055565</v>
+        <v>55.565</v>
       </c>
       <c r="F239" s="5" t="n">
-        <v>0.045527</v>
+        <v>45.527</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
